--- a/admin/e2e/fixtures/files/generic-inventory.xlsx
+++ b/admin/e2e/fixtures/files/generic-inventory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>SKU编码</t>
   </si>
@@ -28,10 +28,10 @@
     <t>参考进价</t>
   </si>
   <si>
-    <t>SKU-X100-BLK</t>
-  </si>
-  <si>
-    <t>WH-MAIN</t>
+    <t>DEMO-SKU-1-1</t>
+  </si>
+  <si>
+    <t>default</t>
   </si>
   <si>
     <t>120</t>
@@ -40,7 +40,10 @@
     <t>45.00</t>
   </si>
   <si>
-    <t>SKU-X100-WHT</t>
+    <t>DEMO-SKU-1-2</t>
+  </si>
+  <si>
+    <t>DEMO-WH-2</t>
   </si>
   <si>
     <t>80</t>
@@ -383,10 +386,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
